--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260622.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.21%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>885,744,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.24%</t>
+          <t>9.93%</t>
         </is>
       </c>
     </row>
@@ -660,227 +660,227 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.98%</t>
+          <t>6.74%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,065,000</t>
+          <t>184,380,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.69%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>184,380,000</t>
+          <t>37,065,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,979,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>112,424,000</t>
+          <t>4,979,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>112,424,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>133,920,945</t>
+          <t>1,966</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>133,920,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,966</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -924,183 +924,183 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>62,290,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>97,767,000</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>348,675,000</t>
+          <t>97,767,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,290,000</t>
+          <t>348,675,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>50,817,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>50,817,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>85,399,080</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>85,399,080</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,978,949,617</t>
+          <t>9,322,726,040</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,014,827,791</t>
+          <t>11,693,552,743</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-2,697,646,041</t>
+          <t>-2,021,935,852</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
